--- a/docs/qa/upload-templates/demand_forecast_upload_template.xlsx
+++ b/docs/qa/upload-templates/demand_forecast_upload_template.xlsx
@@ -141,9 +141,9 @@
         <t>Numeric &gt;= 0</t>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
+    <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>Optional statistical|sales|marketing</t>
+        <t>statistical|sales|marketing</t>
       </text>
     </comment>
   </commentList>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,17 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>uom</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>source</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>confidence_pct</t>
         </is>
       </c>
     </row>
@@ -480,8 +490,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>statistical</t>
         </is>
+      </c>
+      <c r="F2" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="3">
@@ -500,8 +518,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>sales</t>
         </is>
+      </c>
+      <c r="F3" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="4">
@@ -520,8 +546,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>statistical</t>
         </is>
+      </c>
+      <c r="F4" t="n">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
